--- a/German Bundesliga/Y.xlsx
+++ b/German Bundesliga/Y.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2647"/>
+  <dimension ref="A1:C2656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29551,6 +29551,105 @@
         <v>0.3377230730711711</v>
       </c>
     </row>
+    <row r="2648">
+      <c r="A2648" t="n">
+        <v>0.4491368706435606</v>
+      </c>
+      <c r="B2648" t="n">
+        <v>0.2515961408118352</v>
+      </c>
+      <c r="C2648" t="n">
+        <v>0.2992669885446041</v>
+      </c>
+    </row>
+    <row r="2649">
+      <c r="A2649" t="n">
+        <v>0.3681079997326739</v>
+      </c>
+      <c r="B2649" t="n">
+        <v>0.2796899017576689</v>
+      </c>
+      <c r="C2649" t="n">
+        <v>0.3522020985096572</v>
+      </c>
+    </row>
+    <row r="2650">
+      <c r="A2650" t="n">
+        <v>0.3279919271007471</v>
+      </c>
+      <c r="B2650" t="n">
+        <v>0.2611899015811454</v>
+      </c>
+      <c r="C2650" t="n">
+        <v>0.4108181713181074</v>
+      </c>
+    </row>
+    <row r="2651">
+      <c r="A2651" t="n">
+        <v>0.4832911941340643</v>
+      </c>
+      <c r="B2651" t="n">
+        <v>0.2647986170650827</v>
+      </c>
+      <c r="C2651" t="n">
+        <v>0.251910188800853</v>
+      </c>
+    </row>
+    <row r="2652">
+      <c r="A2652" t="n">
+        <v>0.3663742466201858</v>
+      </c>
+      <c r="B2652" t="n">
+        <v>0.2639251517319486</v>
+      </c>
+      <c r="C2652" t="n">
+        <v>0.3697006016478657</v>
+      </c>
+    </row>
+    <row r="2653">
+      <c r="A2653" t="n">
+        <v>0.1739245109529844</v>
+      </c>
+      <c r="B2653" t="n">
+        <v>0.2139806436330791</v>
+      </c>
+      <c r="C2653" t="n">
+        <v>0.6120948454139366</v>
+      </c>
+    </row>
+    <row r="2654">
+      <c r="A2654" t="n">
+        <v>0.8902268091999429</v>
+      </c>
+      <c r="B2654" t="n">
+        <v>0.07675198706345451</v>
+      </c>
+      <c r="C2654" t="n">
+        <v>0.03302120373660253</v>
+      </c>
+    </row>
+    <row r="2655">
+      <c r="A2655" t="n">
+        <v>0.4273024068028244</v>
+      </c>
+      <c r="B2655" t="n">
+        <v>0.2827423885809734</v>
+      </c>
+      <c r="C2655" t="n">
+        <v>0.2899552046162023</v>
+      </c>
+    </row>
+    <row r="2656">
+      <c r="A2656" t="n">
+        <v>0.4880147583207105</v>
+      </c>
+      <c r="B2656" t="n">
+        <v>0.2370938367508119</v>
+      </c>
+      <c r="C2656" t="n">
+        <v>0.2748914049284775</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
